--- a/ProyectoRedes_Claves.xlsx
+++ b/ProyectoRedes_Claves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perci\Escritorio\8vo_Semestre\Redes\ProyectoFinal\ProyectoRedesFI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CABCAE2-FC42-4737-A1CA-59C316B0C849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C823C36-4038-44E7-9352-E8009E0EE7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-2508" windowWidth="23256" windowHeight="12456" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
+    <workbookView xWindow="-23136" yWindow="-2400" windowWidth="11712" windowHeight="12336" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>Contraseñas AP</t>
   </si>
@@ -96,6 +96,45 @@
   </si>
   <si>
     <t>D0CK3R#3</t>
+  </si>
+  <si>
+    <t>Contraseñas SWITCHES</t>
+  </si>
+  <si>
+    <t>Contraseñas ROUTERS</t>
+  </si>
+  <si>
+    <t>CONTRASEÑA [EN]</t>
+  </si>
+  <si>
+    <t>SW_PB</t>
+  </si>
+  <si>
+    <t>SW_SERV</t>
+  </si>
+  <si>
+    <t>SW_P1</t>
+  </si>
+  <si>
+    <t>SW_P3</t>
+  </si>
+  <si>
+    <t>SW_P2</t>
+  </si>
+  <si>
+    <t>R_PB</t>
+  </si>
+  <si>
+    <t>R_P1</t>
+  </si>
+  <si>
+    <t>R_P2</t>
+  </si>
+  <si>
+    <t>R_P3</t>
+  </si>
+  <si>
+    <t>PASSWORD SSH</t>
   </si>
 </sst>
 </file>
@@ -127,7 +166,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -135,17 +174,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,88 +551,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C17A4F0-2BEF-4586-A953-5709064D6E13}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="B3:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="3">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
